--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -569,7 +569,7 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>24940.85</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="3">
@@ -630,7 +630,7 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29060.14</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="4">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21497.76</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="5">
@@ -752,7 +752,7 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>68954.47</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="6">
@@ -813,7 +813,7 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>73205.75</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="7">
@@ -878,7 +878,7 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>220060.09</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="8">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>24052.33</v>
+        <v>23882.59</v>
       </c>
     </row>
     <row r="9">
@@ -1000,7 +1000,7 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>73156.32000000001</v>
+        <v>73851.35000000001</v>
       </c>
     </row>
     <row r="10">
@@ -1061,7 +1061,7 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>61996.23</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="11">
@@ -1122,7 +1122,7 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>33840.08</v>
+        <v>33338.71</v>
       </c>
     </row>
     <row r="12">
@@ -1183,7 +1183,7 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>22445.72</v>
+        <v>22670.48</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M12"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>4232-160-CM25</t>
+          <t>5420-159-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,12 +524,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -539,12 +539,12 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -554,12 +554,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K2" t="inlineStr"/>
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>25371.37</v>
+        <v>35706.78</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4232-159-CM25</t>
+          <t>4232-160-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>29008.6</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2585-4705-CM25</t>
+          <t>4232-159-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>21580.27</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2366-4461-CM25</t>
+          <t>2585-4705-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>69219.13</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2366-4462-CM25</t>
+          <t>2366-4461-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -798,12 +798,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
@@ -813,13 +813,13 @@
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>73486.73</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2369-117-CM25</t>
+          <t>2366-4462-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,17 +829,17 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -859,32 +859,28 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>Región del Ñuble</t>
-        </is>
-      </c>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>218722.92</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>963423-38-CM26</t>
+          <t>2369-117-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -894,27 +890,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -932,35 +928,39 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Región del Ñuble</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>23882.59</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>5420-57-CM26</t>
+          <t>963423-38-CM26</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>Zona de Bienestar Arica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
+          <t>86.519.000-K</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,13 +1000,13 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>73851.35000000001</v>
+        <v>23882.59</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>5420-57-CM26</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1016,12 +1016,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1046,12 +1046,12 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.572.360-9</t>
         </is>
       </c>
       <c r="K10" t="inlineStr"/>
@@ -1061,13 +1061,13 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>62187.89</v>
+        <v>73851.35000000001</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>941739-50-CM26</t>
+          <t>2585-483-CM26</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1082,22 +1082,22 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K11" t="inlineStr"/>
@@ -1122,13 +1122,13 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>33338.71</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>5042-25-CM26</t>
+          <t>941739-50-CM26</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1138,12 +1138,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -1153,12 +1153,12 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,6 +1183,67 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
+        <v>33338.71</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>5042-25-CM26</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>jul-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-07-06</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
         <v>22670.48</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Arica y Parinacota" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -514,7 +514,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>5420-159-CM25</t>
+          <t>941739-21-CM25</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -524,27 +524,27 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>jun-2025</t>
+          <t>feb-2025</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-10</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="M2" s="2" t="n">
-        <v>35706.78</v>
+        <v>69332.92</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>4232-160-CM25</t>
+          <t>1346279-68-CM25</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -585,12 +585,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>mar-2025</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-03-26</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -600,12 +600,12 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>62.000.970-9</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SERVICIO NACIONAL DE REINSERCION SOCIAL JUVENIL</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -615,12 +615,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>AUTOMOTORES GILDEMEISTER SPA</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>79.649.140-k</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
@@ -630,13 +630,13 @@
         </is>
       </c>
       <c r="M3" s="2" t="n">
-        <v>25371.37</v>
+        <v>29340.59</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>4232-159-CM25</t>
+          <t>1489-13-CM25</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -646,12 +646,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>nov-2025</t>
+          <t>abr-2025</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-04-10</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -661,12 +661,12 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>60.505.101-4</t>
+          <t>61.979.110-k</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>SUBSECRETARIA DE SERVICIOS SOCIALES</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -676,12 +676,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>76.005.909-9</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K4" t="inlineStr"/>
@@ -691,13 +691,13 @@
         </is>
       </c>
       <c r="M4" s="2" t="n">
-        <v>29008.6</v>
+        <v>23549.86</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>2585-4705-CM25</t>
+          <t>5420-159-CM25</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -707,12 +707,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jun-2025</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -737,12 +737,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K5" t="inlineStr"/>
@@ -752,13 +752,13 @@
         </is>
       </c>
       <c r="M5" s="2" t="n">
-        <v>21580.27</v>
+        <v>35706.78</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>2366-4461-CM25</t>
+          <t>2369-37-CM25</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>jul-2025</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-07-21</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -798,28 +798,32 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M6" s="2" t="n">
-        <v>69219.13</v>
+        <v>364772.75</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>2366-4462-CM25</t>
+          <t>2585-4029-CM25</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -829,12 +833,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>dic-2025</t>
+          <t>ago-2025</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-08-26</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -859,12 +863,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>MEDITERRANEO AUTOMOTORES S A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>96.889.440-4</t>
         </is>
       </c>
       <c r="K7" t="inlineStr"/>
@@ -874,13 +878,13 @@
         </is>
       </c>
       <c r="M7" s="2" t="n">
-        <v>73486.73</v>
+        <v>34510.01</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>2369-117-CM25</t>
+          <t>4232-160-CM25</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -890,27 +894,27 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>feb-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -920,32 +924,28 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>Región del Ñuble</t>
-        </is>
-      </c>
+          <t>76.005.909-9</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M8" s="2" t="n">
-        <v>218722.92</v>
+        <v>25371.37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>963423-38-CM26</t>
+          <t>4232-159-CM25</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -955,12 +955,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>nov-2025</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>60.505.101-4</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>Carabineros de Chile - Prefectura Arica</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,12 +985,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Maritano y Ebensperger Ltda.</t>
+          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>86.519.000-K</t>
+          <t>76.005.909-9</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
@@ -1000,28 +1000,28 @@
         </is>
       </c>
       <c r="M9" s="2" t="n">
-        <v>23882.59</v>
+        <v>29008.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>5420-57-CM26</t>
+          <t>2366-4461-CM25</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -1031,12 +1031,12 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1061,28 +1061,28 @@
         </is>
       </c>
       <c r="M10" s="2" t="n">
-        <v>73851.35000000001</v>
+        <v>69219.13</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>2585-4705-CM25</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1122,43 +1122,43 @@
         </is>
       </c>
       <c r="M11" s="2" t="n">
-        <v>62187.89</v>
+        <v>21580.27</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>941739-50-CM26</t>
+          <t>2366-4462-CM25</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>dic-2025</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2025-12-15</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1168,12 +1168,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
+          <t>91.502.000-3</t>
         </is>
       </c>
       <c r="K12" t="inlineStr"/>
@@ -1183,68 +1183,438 @@
         </is>
       </c>
       <c r="M12" s="2" t="n">
-        <v>33338.71</v>
+        <v>73486.73</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
+          <t>2369-117-CM25</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>feb-2026</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2026-02-24</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>218722.92</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>963423-38-CM26</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2239-8-LR23</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>mar-2026</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>2026-03-10</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>61.980.850-9</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Zona de Bienestar Arica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Maritano y Ebensperger Ltda.</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>23882.59</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>5420-57-CM26</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>may-2026</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>61.978.890-7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>73851.35000000001</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2585-483-CM26</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>Recepcion Conforme</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>62187.89</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>941739-50-CM26</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>jun-2026</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>70.770.800-K</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>UNIVERSIDAD DE TARAPACA</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>Callegari Ltda.</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>84.916.800-2</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>33338.71</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>5042-25-CM26</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B18" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C13" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>jul-2026</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
+      <c r="D18" t="inlineStr">
         <is>
           <t>2026-07-06</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="E18" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>69.010.100-9</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
         <is>
           <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr">
+      <c r="J18" t="inlineStr">
         <is>
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="n">
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="n">
         <v>22670.48</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5611-72-CM26</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>ago-2026</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2026-08-13</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>61.813.000-2</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>26735.86</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -914,7 +914,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -975,7 +975,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Carabineros de Chile - Prefectura Arica</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -985,7 +985,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>COMERCIAL MOTORES DE LOS ANDES SPA</t>
+          <t>Comercial Motores de los Andes SpA</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Zona de Bienestar Arica</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1518,7 +1518,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1579,7 +1579,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1615,6 +1615,128 @@
       </c>
       <c r="M19" s="2" t="n">
         <v>26735.86</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2585-931-CM26</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>38112.64</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>1546284-2-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-22</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>62.000.890-7</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>COMERCIAL KAUFMANN S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>74856.99000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M21"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr"/>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L2" t="inlineStr">
         <is>
           <t>USD</t>
@@ -623,7 +627,11 @@
           <t>79.649.140-k</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr"/>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L3" t="inlineStr">
         <is>
           <t>USD</t>
@@ -684,7 +692,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr">
         <is>
           <t>USD</t>
@@ -745,7 +757,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr">
         <is>
           <t>USD</t>
@@ -871,7 +887,11 @@
           <t>96.889.440-4</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr"/>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L7" t="inlineStr">
         <is>
           <t>USD</t>
@@ -932,7 +952,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr"/>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L8" t="inlineStr">
         <is>
           <t>USD</t>
@@ -993,7 +1017,11 @@
           <t>76.005.909-9</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr"/>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L9" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1054,7 +1082,11 @@
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr"/>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L10" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1115,7 +1147,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L11" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1176,7 +1212,11 @@
           <t>91.502.000-3</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr"/>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L12" t="inlineStr">
         <is>
           <t>USD</t>
@@ -1189,7 +1229,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>2369-117-CM25</t>
+          <t>2369-128-SE25</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1204,12 +1244,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2026-02-24</t>
+          <t>2026-02-04</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1239,7 +1279,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L13" t="inlineStr">
@@ -1248,13 +1288,13 @@
         </is>
       </c>
       <c r="M13" s="2" t="n">
-        <v>218722.92</v>
+        <v>389190.6</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>963423-38-CM26</t>
+          <t>2369-117-CM25</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1264,27 +1304,27 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>mar-2026</t>
+          <t>feb-2026</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>61.980.850-9</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -1302,35 +1342,39 @@
           <t>86.519.000-K</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr"/>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L14" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M14" s="2" t="n">
-        <v>23882.59</v>
+        <v>218722.92</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>5420-57-CM26</t>
+          <t>963423-38-CM26</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2239-6-LR25</t>
+          <t>2239-8-LR23</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>may-2026</t>
+          <t>mar-2026</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1340,12 +1384,12 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>61.978.890-7</t>
+          <t>61.980.850-9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
@@ -1355,28 +1399,32 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>Maritano y Ebensperger Ltda.</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr"/>
+          <t>86.519.000-K</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L15" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M15" s="2" t="n">
-        <v>73851.35000000001</v>
+        <v>23882.59</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>2585-483-CM26</t>
+          <t>5420-57-CM26</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1386,12 +1434,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>jun-2026</t>
+          <t>may-2026</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1401,12 +1449,12 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.978.890-7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>GOBIERNO REGIONAL DE ARICA-PARINACOTA</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
@@ -1416,28 +1464,32 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L16" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M16" s="2" t="n">
-        <v>62187.89</v>
+        <v>73851.35000000001</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>941739-50-CM26</t>
+          <t>2585-483-CM26</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1452,22 +1504,22 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>2026-06-26</t>
+          <t>2026-06-22</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>70.770.800-K</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
@@ -1477,28 +1529,32 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Callegari Ltda.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>84.916.800-2</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L17" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M17" s="2" t="n">
-        <v>33338.71</v>
+        <v>62187.89</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>5042-25-CM26</t>
+          <t>941739-50-CM26</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1508,27 +1564,27 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>jul-2026</t>
+          <t>jun-2026</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>2026-07-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>70.770.800-K</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
@@ -1538,12 +1594,12 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+          <t>Callegari Ltda.</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>91.502.000-3</t>
+          <t>84.916.800-2</t>
         </is>
       </c>
       <c r="K18" t="inlineStr"/>
@@ -1553,13 +1609,13 @@
         </is>
       </c>
       <c r="M18" s="2" t="n">
-        <v>22670.48</v>
+        <v>33338.71</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>5611-72-CM26</t>
+          <t>5042-25-CM26</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1569,12 +1625,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ago-2026</t>
+          <t>jul-2026</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2026-08-13</t>
+          <t>2026-07-06</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1584,12 +1640,12 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>61.813.000-2</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1599,28 +1655,32 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>COMERCIAL KAUFMANN S.A.</t>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>96.572.360-9</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr"/>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
       <c r="L19" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M19" s="2" t="n">
-        <v>26735.86</v>
+        <v>22670.48</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>2585-931-CM26</t>
+          <t>5611-72-CM26</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1630,27 +1690,27 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>sep-2026</t>
+          <t>ago-2026</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.813.000-2</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>SERVICIO REGIONAL DE LA VIVIENDA Y URBAN</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1660,82 +1720,155 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>BRUNO FRITSCH S.A.</t>
+          <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>84.807.200-1</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr"/>
+          <t>96.572.360-9</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L20" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M20" s="2" t="n">
-        <v>38112.64</v>
+        <v>26735.86</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
+          <t>2585-931-CM26</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>sep-2026</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>BRUNO FRITSCH S.A.</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>84.807.200-1</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>38112.64</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
           <t>1546284-2-CM26</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B22" t="inlineStr">
         <is>
           <t>2239-6-LR25</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>sep-2026</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr">
+      <c r="D22" t="inlineStr">
         <is>
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="E22" t="inlineStr">
         <is>
           <t>Aceptada</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>62.000.890-7</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>SERVICIO NACIONAL DE PROTECCIÓN ESPECIALIZADA A LA NIÑEZ Y ADOLESCENCI</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>Arica y Parinacota</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
         <is>
           <t>COMERCIAL KAUFMANN S.A.</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr">
+      <c r="J22" t="inlineStr">
         <is>
           <t>96.572.360-9</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>USD</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="n">
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="n">
         <v>74856.99000000001</v>
       </c>
     </row>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -1602,7 +1602,11 @@
           <t>84.916.800-2</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>Coquimbo</t>
+        </is>
+      </c>
       <c r="L18" t="inlineStr">
         <is>
           <t>USD</t>

--- a/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
+++ b/docs/oc-regiones/adquisicion-de-vehiculos-y-maquinaria/arica-y-parinacota.xlsx
@@ -426,7 +426,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M22"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1876,6 +1876,71 @@
         <v>74856.99000000001</v>
       </c>
     </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2369-149-CM26</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2239-6-LR25</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>oct-2026</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>2026-10-21</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>Aceptada</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>69.010.100-9</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>I MUNICIPALIDAD DE ARICA</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Arica y Parinacota</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>SALINAS Y FABRES SOCIEDAD ANONIMA</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>91.502.000-3</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>Antofagasta</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>43706.87</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
